--- a/471/food/2026-02-18-sm.xlsx
+++ b/471/food/2026-02-18-sm.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.»</t>
+          <t xml:space="preserve">МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.» </t>
         </is>
       </c>
       <c r="C1" s="37" t="n"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
